--- a/artfynd/A 44460-2023 artfynd.xlsx
+++ b/artfynd/A 44460-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44460-2023 artfynd.xlsx
+++ b/artfynd/A 44460-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112492034</v>
+        <v>112491605</v>
       </c>
       <c r="B2" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356931</v>
+        <v>356851</v>
       </c>
       <c r="R2" t="n">
-        <v>6741729</v>
+        <v>6741779</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,49 +764,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112491953</v>
+        <v>112491706</v>
       </c>
       <c r="B3" t="n">
-        <v>77772</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356916</v>
+        <v>356993</v>
       </c>
       <c r="R3" t="n">
-        <v>6741711</v>
+        <v>6742004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,27 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112492403</v>
+        <v>112492199</v>
       </c>
       <c r="B4" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>357062</v>
+        <v>356836</v>
       </c>
       <c r="R4" t="n">
-        <v>6741938</v>
+        <v>6741812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112492407</v>
+        <v>112491622</v>
       </c>
       <c r="B5" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>357062</v>
+        <v>356917</v>
       </c>
       <c r="R5" t="n">
-        <v>6741938</v>
+        <v>6741847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,27 +1067,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112491951</v>
+        <v>112492390</v>
       </c>
       <c r="B6" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1142,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>356916</v>
+        <v>357000</v>
       </c>
       <c r="R6" t="n">
-        <v>6741711</v>
+        <v>6741919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112492031</v>
+        <v>112491606</v>
       </c>
       <c r="B7" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>356931</v>
+        <v>356851</v>
       </c>
       <c r="R7" t="n">
-        <v>6741729</v>
+        <v>6741779</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,27 +1269,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112492380</v>
+        <v>112491611</v>
       </c>
       <c r="B8" t="n">
-        <v>56658</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,27 +1292,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1355,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>356973</v>
+        <v>356792</v>
       </c>
       <c r="R8" t="n">
-        <v>6741867</v>
+        <v>6741655</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,6 +1367,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1417,15 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112492199</v>
+        <v>112492391</v>
       </c>
       <c r="B9" t="n">
-        <v>89586</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1433,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1460,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>356836</v>
+        <v>357000</v>
       </c>
       <c r="R9" t="n">
-        <v>6741812</v>
+        <v>6741919</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,37 +1487,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112492391</v>
+        <v>112491953</v>
       </c>
       <c r="B10" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1525,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>356999</v>
+        <v>356916</v>
       </c>
       <c r="R10" t="n">
-        <v>6741919</v>
+        <v>6741712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,15 +1588,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112492388</v>
+        <v>112491460</v>
       </c>
       <c r="B11" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1645,21 +1599,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1672,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>356999</v>
+        <v>356953</v>
       </c>
       <c r="R11" t="n">
-        <v>6741919</v>
+        <v>6741607</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,49 +1677,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112491622</v>
+        <v>112491798</v>
       </c>
       <c r="B12" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1778,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>356918</v>
+        <v>356909</v>
       </c>
       <c r="R12" t="n">
-        <v>6741847</v>
+        <v>6741618</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,56 +1778,47 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112491611</v>
+        <v>112492031</v>
       </c>
       <c r="B13" t="n">
-        <v>90934</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1888,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>356793</v>
+        <v>356931</v>
       </c>
       <c r="R13" t="n">
-        <v>6741655</v>
+        <v>6741728</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,15 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112491562</v>
+        <v>112492069</v>
       </c>
       <c r="B14" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>356900</v>
+        <v>356836</v>
       </c>
       <c r="R14" t="n">
-        <v>6741677</v>
+        <v>6741812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,56 +1980,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112492359</v>
+        <v>112492407</v>
       </c>
       <c r="B15" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2102,10 +2030,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>356906</v>
+        <v>357062</v>
       </c>
       <c r="R15" t="n">
-        <v>6741839</v>
+        <v>6741939</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,15 +2093,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112492065</v>
+        <v>112491886</v>
       </c>
       <c r="B16" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,25 +2104,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>102613</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2210,10 +2132,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>356836</v>
+        <v>356977</v>
       </c>
       <c r="R16" t="n">
-        <v>6741812</v>
+        <v>6741588</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,7 +2176,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2273,15 +2194,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112491798</v>
+        <v>112491891</v>
       </c>
       <c r="B17" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2289,26 +2205,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2316,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>356909</v>
+        <v>356977</v>
       </c>
       <c r="R17" t="n">
-        <v>6741618</v>
+        <v>6741588</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2360,7 +2277,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2379,15 +2295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112491460</v>
+        <v>112492380</v>
       </c>
       <c r="B18" t="n">
-        <v>77149</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,26 +2306,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6437</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2422,10 +2334,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>356953</v>
+        <v>356973</v>
       </c>
       <c r="R18" t="n">
-        <v>6741607</v>
+        <v>6741867</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,61 +2378,57 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112491468</v>
+        <v>112491646</v>
       </c>
       <c r="B19" t="n">
-        <v>77499</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2528,10 +2436,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>356953</v>
+        <v>356792</v>
       </c>
       <c r="R19" t="n">
-        <v>6741607</v>
+        <v>6741655</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,54 +2487,51 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112492069</v>
+        <v>112491720</v>
       </c>
       <c r="B20" t="n">
-        <v>78338</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2634,10 +2539,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>356836</v>
+        <v>356878</v>
       </c>
       <c r="R20" t="n">
-        <v>6741812</v>
+        <v>6741663</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2697,15 +2602,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112491646</v>
+        <v>112492065</v>
       </c>
       <c r="B21" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2742,10 +2642,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>356793</v>
+        <v>356836</v>
       </c>
       <c r="R21" t="n">
-        <v>6741655</v>
+        <v>6741812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,42 +2705,39 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112491455</v>
+        <v>112492359</v>
       </c>
       <c r="B22" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2848,10 +2745,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>356953</v>
+        <v>356905</v>
       </c>
       <c r="R22" t="n">
-        <v>6741607</v>
+        <v>6741839</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2899,49 +2796,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112492390</v>
+        <v>112491468</v>
       </c>
       <c r="B23" t="n">
-        <v>90922</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2954,10 +2846,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>356999</v>
+        <v>356953</v>
       </c>
       <c r="R23" t="n">
-        <v>6741919</v>
+        <v>6741607</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3005,56 +2897,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112491720</v>
+        <v>112491562</v>
       </c>
       <c r="B24" t="n">
-        <v>8424</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3062,10 +2947,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>356878</v>
+        <v>356899</v>
       </c>
       <c r="R24" t="n">
-        <v>6741663</v>
+        <v>6741678</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3113,27 +2998,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>August Oljeqvist, Jonas Göransson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112491706</v>
+        <v>112491951</v>
       </c>
       <c r="B25" t="n">
-        <v>90938</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3141,21 +3021,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3168,10 +3048,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>356993</v>
+        <v>356916</v>
       </c>
       <c r="R25" t="n">
-        <v>6742004</v>
+        <v>6741712</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3219,27 +3099,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>August Oljeqvist, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112491947</v>
+        <v>112492034</v>
       </c>
       <c r="B26" t="n">
-        <v>78312</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3247,21 +3122,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3274,10 +3149,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>356916</v>
+        <v>356931</v>
       </c>
       <c r="R26" t="n">
-        <v>6741711</v>
+        <v>6741728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3334,6 +3209,410 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>112492388</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kroktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>357000</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6741919</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Södra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>112492403</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kroktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>357062</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6741939</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Södra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>112491455</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kroktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>356953</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6741607</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Södra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>112491947</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kroktjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>356916</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6741712</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Södra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-10-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44460-2023 artfynd.xlsx
+++ b/artfynd/A 44460-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491605</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492199</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491622</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492390</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491611</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492391</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1585,6 +1630,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491953</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1686,6 +1736,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491460</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491798</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492031</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1989,6 +2054,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492069</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492407</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491886</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491891</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492380</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2496,6 +2586,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491646</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2599,6 +2694,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491720</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2702,6 +2802,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492065</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2805,6 +2910,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492359</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2906,6 +3016,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491468</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3007,6 +3122,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3108,6 +3228,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491951</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3209,6 +3334,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492034</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3310,6 +3440,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492388</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3411,6 +3546,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492403</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3512,6 +3652,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491455</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3613,8 +3758,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491947</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>